--- a/data/trans_camb/P57GLOBAL_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P57GLOBAL_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 5,4</t>
+          <t>-6,96; 5,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,95; 21,92</t>
+          <t>10,67; 22,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-25,37; -5,18</t>
+          <t>-24,83; -5,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 9,19</t>
+          <t>-3,47; 8,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,75; 22,52</t>
+          <t>10,62; 22,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-22,79; -5,13</t>
+          <t>-23,08; -5,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 6,0</t>
+          <t>-3,22; 5,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,51; 20,87</t>
+          <t>12,2; 21,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-21,6; -7,81</t>
+          <t>-21,2; -7,91</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 9,41</t>
+          <t>-10,77; 9,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,2; 37,75</t>
+          <t>16,44; 40,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-40,42; -8,77</t>
+          <t>-39,05; -9,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 15,11</t>
+          <t>-5,21; 14,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,42; 38,32</t>
+          <t>15,72; 37,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,2; -8,28</t>
+          <t>-36,27; -8,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 9,56</t>
+          <t>-4,94; 9,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,5; 34,89</t>
+          <t>18,82; 35,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-34,24; -13,12</t>
+          <t>-33,63; -12,93</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 2,65</t>
+          <t>-7,39; 2,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,78; 18,52</t>
+          <t>8,85; 18,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,82; 1,92</t>
+          <t>-12,63; 1,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 8,51</t>
+          <t>-1,69; 8,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,42; 16,29</t>
+          <t>6,52; 16,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-37,8; -11,89</t>
+          <t>-42,27; -11,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 3,98</t>
+          <t>-3,16; 4,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,69; 16,51</t>
+          <t>9,52; 16,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-27,52; -8,01</t>
+          <t>-26,64; -7,78</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,37; 4,07</t>
+          <t>-10,54; 4,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,46; 28,68</t>
+          <t>12,38; 28,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,46; 3,0</t>
+          <t>-18,14; 2,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 12,68</t>
+          <t>-2,29; 13,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,97; 24,56</t>
+          <t>9,14; 24,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,49; -17,2</t>
+          <t>-57,8; -17,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 5,98</t>
+          <t>-4,45; 6,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,74; 24,74</t>
+          <t>13,6; 24,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-40,32; -11,87</t>
+          <t>-38,35; -11,65</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 6,13</t>
+          <t>-3,83; 6,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,45; 16,66</t>
+          <t>7,31; 16,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,92; -1,6</t>
+          <t>-12,78; -1,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 9,23</t>
+          <t>-0,35; 9,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,78; 15,87</t>
+          <t>6,85; 16,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,64; -5,39</t>
+          <t>-14,77; -5,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 6,41</t>
+          <t>-0,64; 6,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,42; 15,25</t>
+          <t>8,27; 15,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,58; -4,78</t>
+          <t>-12,68; -5,14</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 9,03</t>
+          <t>-5,2; 9,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,36; 24,87</t>
+          <t>10,1; 25,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-17,88; -2,34</t>
+          <t>-17,78; -2,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 13,49</t>
+          <t>-0,48; 14,06</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,12; 23,38</t>
+          <t>9,23; 23,3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-21,4; -7,9</t>
+          <t>-20,55; -7,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 9,38</t>
+          <t>-0,82; 9,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,59; 22,19</t>
+          <t>11,46; 22,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-17,21; -6,83</t>
+          <t>-17,44; -7,5</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 2,89</t>
+          <t>-7,7; 3,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,19; 14,52</t>
+          <t>4,46; 14,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-55,04; -8,27</t>
+          <t>-55,48; -8,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,82; 13,8</t>
+          <t>4,3; 14,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,59; 19,47</t>
+          <t>9,78; 19,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-17,64; -2,67</t>
+          <t>-18,18; -2,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 7,18</t>
+          <t>-0,32; 7,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,12; 15,28</t>
+          <t>8,11; 15,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-40,32; -7,49</t>
+          <t>-39,28; -7,95</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 4,04</t>
+          <t>-10,26; 4,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,55; 21,08</t>
+          <t>5,87; 21,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-72,52; -11,46</t>
+          <t>-73,65; -11,18</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,12; 20,22</t>
+          <t>5,71; 20,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,06; 29,12</t>
+          <t>13,22; 28,76</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-24,0; -3,98</t>
+          <t>-25,32; -4,49</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 10,23</t>
+          <t>-0,43; 10,01</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,85; 21,78</t>
+          <t>10,81; 21,72</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-55,06; -10,41</t>
+          <t>-53,24; -11,14</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-11,71; 1,48</t>
+          <t>-12,14; 1,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,59; 17,43</t>
+          <t>5,18; 16,26</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 2,49</t>
+          <t>-10,08; 1,79</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 3,71</t>
+          <t>-8,66; 3,09</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,96; 15,09</t>
+          <t>4,55; 14,7</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 0,73</t>
+          <t>-9,53; 0,51</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 0,77</t>
+          <t>-7,77; 0,51</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,33; 14,07</t>
+          <t>6,41; 14,14</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-8,03; -0,06</t>
+          <t>-8,47; -0,67</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-15,78; 2,07</t>
+          <t>-15,85; 2,7</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>7,46; 25,54</t>
+          <t>6,79; 23,66</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-12,76; 3,57</t>
+          <t>-13,24; 2,67</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 4,8</t>
+          <t>-10,81; 4,23</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>6,25; 20,66</t>
+          <t>5,77; 20,19</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-11,47; 0,91</t>
+          <t>-11,76; 0,69</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-10,99; 1,03</t>
+          <t>-10,13; 0,68</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>8,15; 19,46</t>
+          <t>8,43; 19,64</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-10,31; -0,07</t>
+          <t>-10,86; -0,69</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 3,75</t>
+          <t>-10,59; 3,36</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 8,95</t>
+          <t>-3,57; 9,59</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-16,98; -4,65</t>
+          <t>-16,78; -4,54</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 5,15</t>
+          <t>-6,95; 5,49</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,68; 17,1</t>
+          <t>6,86; 16,66</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-16,21; -5,98</t>
+          <t>-16,34; -5,32</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 2,27</t>
+          <t>-6,84; 2,64</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>3,2; 11,55</t>
+          <t>3,22; 11,49</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-15,25; -7,01</t>
+          <t>-14,68; -6,49</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-12,84; 4,85</t>
+          <t>-13,05; 4,43</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 12,14</t>
+          <t>-4,49; 13,04</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-20,65; -6,14</t>
+          <t>-20,56; -6,01</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 6,83</t>
+          <t>-8,58; 7,29</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>8,24; 22,94</t>
+          <t>8,51; 22,35</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-19,71; -7,94</t>
+          <t>-20,16; -7,4</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 3,0</t>
+          <t>-8,55; 3,47</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3,98; 15,12</t>
+          <t>3,99; 15,21</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-19,02; -9,18</t>
+          <t>-18,15; -8,48</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 4,46</t>
+          <t>-10,99; 4,3</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 11,3</t>
+          <t>-2,02; 11,39</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-15,32; -1,35</t>
+          <t>-15,67; -1,9</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 3,8</t>
+          <t>-8,83; 3,45</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,49; 13,73</t>
+          <t>2,77; 13,48</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-11,5; -0,48</t>
+          <t>-11,55; -0,48</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 1,66</t>
+          <t>-8,1; 1,4</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2,38; 10,94</t>
+          <t>2,37; 10,74</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-11,28; -3,4</t>
+          <t>-11,61; -3,18</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 5,82</t>
+          <t>-12,98; 5,7</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 14,75</t>
+          <t>-2,33; 14,8</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-18,07; -1,75</t>
+          <t>-18,53; -2,65</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 4,77</t>
+          <t>-10,43; 4,4</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2,93; 17,9</t>
+          <t>3,34; 17,19</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-13,44; -0,59</t>
+          <t>-13,55; -0,85</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-9,84; 2,06</t>
+          <t>-9,62; 1,82</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2,84; 13,83</t>
+          <t>2,79; 13,56</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-13,37; -4,25</t>
+          <t>-13,73; -4,09</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 0,68</t>
+          <t>-3,95; 0,71</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>9,39; 13,82</t>
+          <t>9,49; 13,74</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-25,26; -6,42</t>
+          <t>-26,27; -6,62</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,99; 5,2</t>
+          <t>1,11; 5,15</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>10,43; 14,45</t>
+          <t>10,49; 14,48</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-13,74; -6,81</t>
+          <t>-14,6; -7,22</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,31</t>
+          <t>-0,85; 2,35</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>10,6; 13,41</t>
+          <t>10,54; 13,35</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-19,1; -7,57</t>
+          <t>-19,12; -7,77</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 0,98</t>
+          <t>-5,51; 1,04</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>13,08; 20,09</t>
+          <t>13,19; 19,84</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-35,96; -9,21</t>
+          <t>-37,49; -9,43</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1,34; 7,32</t>
+          <t>1,5; 7,2</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>14,24; 20,41</t>
+          <t>14,2; 20,41</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-18,93; -9,53</t>
+          <t>-20,15; -10,19</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 3,28</t>
+          <t>-1,16; 3,3</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>14,65; 18,99</t>
+          <t>14,59; 18,99</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-26,82; -10,67</t>
+          <t>-26,85; -10,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P57GLOBAL_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P57GLOBAL_R-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-15,25</t>
+          <t>-13,41</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-14,23</t>
+          <t>-11,51</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-14,91</t>
+          <t>-12,56</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 5,68</t>
+          <t>-6,97; 6,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,67; 22,92</t>
+          <t>10,7; 22,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-24,83; -5,55</t>
+          <t>-22,3; -4,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 8,48</t>
+          <t>-4,28; 8,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,62; 22,05</t>
+          <t>10,36; 22,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-23,08; -5,11</t>
+          <t>-20,49; -2,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 5,7</t>
+          <t>-3,41; 5,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,2; 21,01</t>
+          <t>12,25; 20,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-21,2; -7,91</t>
+          <t>-19,23; -6,48</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-24,92%</t>
+          <t>-21,9%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-22,53%</t>
+          <t>-18,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-23,98%</t>
+          <t>-20,2%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,77; 9,79</t>
+          <t>-10,7; 10,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,44; 40,32</t>
+          <t>16,54; 39,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-39,05; -9,18</t>
+          <t>-35,75; -7,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 14,26</t>
+          <t>-6,54; 13,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,72; 37,08</t>
+          <t>15,54; 36,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,27; -8,97</t>
+          <t>-31,02; -4,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 9,6</t>
+          <t>-5,32; 9,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,82; 35,22</t>
+          <t>18,97; 34,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-33,63; -12,93</t>
+          <t>-30,39; -10,86</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-5,21</t>
+          <t>-3,53</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-21,79</t>
+          <t>-12,58</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-14,15</t>
+          <t>-8,08</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 2,8</t>
+          <t>-7,83; 2,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,85; 18,42</t>
+          <t>8,91; 17,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 1,39</t>
+          <t>-10,8; 3,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 8,96</t>
+          <t>-1,79; 8,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,52; 16,16</t>
+          <t>6,71; 16,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-42,27; -11,99</t>
+          <t>-18,5; -6,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 4,07</t>
+          <t>-3,05; 3,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,52; 16,28</t>
+          <t>9,35; 15,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-26,64; -7,78</t>
+          <t>-12,73; -3,47</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-7,68%</t>
+          <t>-5,2%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-31,43%</t>
+          <t>-18,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-20,65%</t>
+          <t>-11,79%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,54; 4,28</t>
+          <t>-11,24; 3,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,38; 28,18</t>
+          <t>12,6; 27,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,14; 2,16</t>
+          <t>-15,37; 4,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 13,69</t>
+          <t>-2,46; 13,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,14; 24,35</t>
+          <t>9,42; 24,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-57,8; -17,38</t>
+          <t>-26,11; -9,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 6,18</t>
+          <t>-4,35; 5,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,6; 24,32</t>
+          <t>13,23; 23,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-38,35; -11,65</t>
+          <t>-18,1; -5,08</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-7,29</t>
+          <t>-5,16</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-10,35</t>
+          <t>-8,6</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-8,85</t>
+          <t>-6,9</t>
         </is>
       </c>
     </row>
@@ -1109,32 +1109,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 6,36</t>
+          <t>-4,15; 6,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,31; 16,66</t>
+          <t>7,44; 17,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,78; -1,52</t>
+          <t>-10,58; 0,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 9,61</t>
+          <t>-0,48; 9,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,85; 16,05</t>
+          <t>6,59; 15,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,77; -5,12</t>
+          <t>-13,74; -3,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,27; 15,2</t>
+          <t>8,47; 14,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,68; -5,14</t>
+          <t>-11,01; -3,18</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-10,36%</t>
+          <t>-7,34%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-14,54%</t>
+          <t>-12,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-12,5%</t>
+          <t>-9,76%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 9,51</t>
+          <t>-5,67; 9,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,1; 25,01</t>
+          <t>10,32; 26,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-17,78; -2,33</t>
+          <t>-14,64; 0,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 14,06</t>
+          <t>-0,62; 14,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,23; 23,3</t>
+          <t>9,11; 23,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-20,55; -7,8</t>
+          <t>-18,64; -5,72</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 9,49</t>
+          <t>-0,87; 9,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,46; 22,04</t>
+          <t>11,64; 21,51</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-17,44; -7,5</t>
+          <t>-15,24; -4,57</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-27,51</t>
+          <t>-9,16</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-8,71</t>
+          <t>-5,24</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-19,07</t>
+          <t>-7,18</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 3,26</t>
+          <t>-7,92; 3,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,46; 14,93</t>
+          <t>4,39; 14,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-55,48; -8,06</t>
+          <t>-14,83; -3,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,3; 14,05</t>
+          <t>3,61; 14,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,78; 19,54</t>
+          <t>9,59; 19,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,18; -2,96</t>
+          <t>-10,18; -0,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 7,02</t>
+          <t>-0,33; 7,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,11; 15,39</t>
+          <t>8,5; 15,78</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-39,28; -7,95</t>
+          <t>-10,72; -3,59</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-37,69%</t>
+          <t>-12,56%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-12,21%</t>
+          <t>-7,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-26,44%</t>
+          <t>-9,95%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 4,44</t>
+          <t>-10,53; 5,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,87; 21,43</t>
+          <t>5,81; 21,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-73,65; -11,18</t>
+          <t>-19,41; -5,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,71; 20,51</t>
+          <t>4,92; 21,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,22; 28,76</t>
+          <t>12,75; 28,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-25,32; -4,49</t>
+          <t>-13,75; -0,6</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 10,01</t>
+          <t>-0,44; 10,44</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,81; 21,72</t>
+          <t>11,38; 22,52</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-53,24; -11,14</t>
+          <t>-14,38; -5,18</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-4,0</t>
+          <t>-3,31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-4,67</t>
+          <t>-4,27</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-4,43</t>
+          <t>-3,86</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,14; 1,76</t>
+          <t>-11,81; 1,92</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,18; 16,26</t>
+          <t>5,55; 16,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 1,79</t>
+          <t>-8,84; 2,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 3,09</t>
+          <t>-8,46; 3,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,55; 14,7</t>
+          <t>4,63; 14,64</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 0,51</t>
+          <t>-9,14; 1,22</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 0,51</t>
+          <t>-8,49; 1,03</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,41; 14,14</t>
+          <t>6,37; 14,31</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-8,47; -0,67</t>
+          <t>-7,54; -0,39</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-5,53%</t>
+          <t>-4,58%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-6,03%</t>
+          <t>-5,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-5,91%</t>
+          <t>-5,16%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-15,85; 2,7</t>
+          <t>-15,72; 2,84</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>6,79; 23,66</t>
+          <t>7,38; 24,24</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-13,24; 2,67</t>
+          <t>-11,78; 4,26</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-10,81; 4,23</t>
+          <t>-10,45; 5,18</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>5,77; 20,19</t>
+          <t>5,86; 19,95</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 0,69</t>
+          <t>-11,44; 1,69</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 0,68</t>
+          <t>-11,08; 1,42</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>8,43; 19,64</t>
+          <t>8,56; 19,91</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-10,86; -0,69</t>
+          <t>-9,71; -0,53</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-10,71</t>
+          <t>-10,61</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-11,09</t>
+          <t>-10,65</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-10,92</t>
+          <t>-10,64</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 3,36</t>
+          <t>-10,85; 3,47</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 9,59</t>
+          <t>-4,25; 9,45</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-16,78; -4,54</t>
+          <t>-16,8; -4,05</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 5,49</t>
+          <t>-6,64; 5,65</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,86; 16,66</t>
+          <t>6,48; 16,77</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-16,34; -5,32</t>
+          <t>-15,57; -4,94</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 2,64</t>
+          <t>-6,54; 2,67</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>3,22; 11,49</t>
+          <t>3,29; 11,38</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-14,68; -6,49</t>
+          <t>-14,59; -6,6</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-13,75%</t>
+          <t>-13,61%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-14,14%</t>
+          <t>-13,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-13,96%</t>
+          <t>-13,61%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 4,43</t>
+          <t>-13,24; 4,61</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 13,04</t>
+          <t>-5,13; 12,6</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-20,56; -6,01</t>
+          <t>-20,69; -5,57</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 7,29</t>
+          <t>-8,2; 7,61</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>8,51; 22,35</t>
+          <t>8,1; 22,56</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-20,16; -7,4</t>
+          <t>-19,1; -6,63</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 3,47</t>
+          <t>-8,2; 3,49</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3,99; 15,21</t>
+          <t>4,1; 15,0</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-18,15; -8,48</t>
+          <t>-18,02; -8,63</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-8,97</t>
+          <t>-8,6</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-6,45</t>
+          <t>-6,48</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-7,46</t>
+          <t>-7,34</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-10,99; 4,3</t>
+          <t>-11,07; 4,19</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 11,39</t>
+          <t>-1,66; 11,32</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-15,67; -1,9</t>
+          <t>-15,53; -1,22</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 3,45</t>
+          <t>-9,38; 3,1</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,77; 13,48</t>
+          <t>2,78; 13,51</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-11,55; -0,48</t>
+          <t>-11,51; -0,89</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 1,4</t>
+          <t>-7,86; 1,75</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2,37; 10,74</t>
+          <t>2,21; 10,9</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-11,61; -3,18</t>
+          <t>-11,65; -2,98</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-11,05%</t>
+          <t>-10,6%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-7,87%</t>
+          <t>-7,91%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-9,13%</t>
+          <t>-8,98%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 5,7</t>
+          <t>-12,73; 5,42</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 14,8</t>
+          <t>-1,93; 14,87</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-18,53; -2,65</t>
+          <t>-18,38; -1,77</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 4,4</t>
+          <t>-10,89; 3,92</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>3,34; 17,19</t>
+          <t>3,19; 17,32</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-13,55; -0,85</t>
+          <t>-13,62; -1,21</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 1,82</t>
+          <t>-9,4; 2,25</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2,79; 13,56</t>
+          <t>2,63; 13,8</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-13,73; -4,09</t>
+          <t>-14,03; -3,82</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-11,9</t>
+          <t>-6,1</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-9,75</t>
+          <t>-6,98</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-10,85</t>
+          <t>-6,54</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 0,71</t>
+          <t>-3,8; 0,71</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>9,49; 13,74</t>
+          <t>9,25; 13,44</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-26,27; -6,62</t>
+          <t>-8,36; -3,73</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1,11; 5,15</t>
+          <t>1,0; 5,23</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>10,49; 14,48</t>
+          <t>10,56; 14,63</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-14,6; -7,22</t>
+          <t>-8,99; -4,95</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 2,35</t>
+          <t>-0,68; 2,4</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>10,54; 13,35</t>
+          <t>10,47; 13,41</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-19,12; -7,77</t>
+          <t>-8,32; -4,99</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-16,89%</t>
+          <t>-8,66%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-13,49%</t>
+          <t>-9,65%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-15,2%</t>
+          <t>-9,16%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 1,04</t>
+          <t>-5,29; 1,02</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>13,19; 19,84</t>
+          <t>12,92; 19,52</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-37,49; -9,43</t>
+          <t>-11,67; -5,35</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1,5; 7,2</t>
+          <t>1,37; 7,38</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>14,2; 20,41</t>
+          <t>14,37; 20,64</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-20,15; -10,19</t>
+          <t>-12,3; -6,94</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 3,3</t>
+          <t>-0,94; 3,39</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>14,59; 18,99</t>
+          <t>14,49; 18,99</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-26,85; -10,96</t>
+          <t>-11,53; -7,05</t>
         </is>
       </c>
     </row>
